--- a/backend/FINAL_ENTERPRISE_OPPORTUNITY_LEDGER.xlsx
+++ b/backend/FINAL_ENTERPRISE_OPPORTUNITY_LEDGER.xlsx
@@ -744,16 +744,16 @@
         <v>TOTAL PORTFOLIO WATERFALL</v>
       </c>
       <c r="B6">
-        <v>323.27</v>
+        <v>173.12</v>
       </c>
       <c r="C6">
-        <v>79.52</v>
+        <v>62.8</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>16.72</v>
       </c>
       <c r="E6">
-        <v>243.75</v>
+        <v>93.6</v>
       </c>
       <c r="F6" t="str">
         <v>VARIANCE INR 0.00</v>
